--- a/output/Summary_Sunking_Pacific_2026-08-12.xlsx
+++ b/output/Summary_Sunking_Pacific_2026-08-12.xlsx
@@ -676,11 +676,11 @@
       </c>
       <c r="C5" s="6">
         <f>SUMIF(Detail!$A$6:$A$10,$A5,Detail!$G$6:$G$10)</f>
-        <v/>
+        <v>651</v>
       </c>
       <c r="D5" s="7">
         <f>SUMIF(Detail!$A$6:$A$10,$A5,Detail!$H$6:$H$10)</f>
-        <v/>
+        <v>2213.4</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -706,11 +706,11 @@
       </c>
       <c r="C6" s="6">
         <f>SUMIF(Detail!$A$6:$A$10,$A6,Detail!$G$6:$G$10)</f>
-        <v/>
+        <v>256</v>
       </c>
       <c r="D6" s="7">
         <f>SUMIF(Detail!$A$6:$A$10,$A6,Detail!$H$6:$H$10)</f>
-        <v/>
+        <v>665.6</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -736,11 +736,11 @@
       </c>
       <c r="C7" s="6">
         <f>SUMIF(Detail!$A$6:$A$10,$A7,Detail!$G$6:$G$10)</f>
-        <v/>
+        <v>64</v>
       </c>
       <c r="D7" s="7">
         <f>SUMIF(Detail!$A$6:$A$10,$A7,Detail!$H$6:$H$10)</f>
-        <v/>
+        <v>192</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -762,11 +762,11 @@
       <c r="B8" s="11" t="n"/>
       <c r="C8" s="12">
         <f>SUM(C5:C7)</f>
-        <v/>
+        <v>971</v>
       </c>
       <c r="D8" s="13">
         <f>SUM(D5:D7)</f>
-        <v/>
+        <v>3071</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
@@ -1113,11 +1113,11 @@
       <c r="F11" s="26" t="n"/>
       <c r="G11" s="27">
         <f>SUM(G6:G10)</f>
-        <v/>
+        <v>971</v>
       </c>
       <c r="H11" s="28">
         <f>SUM(H6:H10)</f>
-        <v/>
+        <v>3071</v>
       </c>
       <c r="I11" s="26" t="n"/>
     </row>
